--- a/Test Sonuclari/TestSonuclari.xlsx
+++ b/Test Sonuclari/TestSonuclari.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -441,16 +441,16 @@
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="45" customWidth="1" min="19" max="19"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="21" max="21"/>
     <col width="45" customWidth="1" min="22" max="22"/>
     <col width="45" customWidth="1" min="23" max="23"/>
     <col width="45" customWidth="1" min="24" max="24"/>
@@ -459,7 +459,7 @@
     <col width="45" customWidth="1" min="27" max="27"/>
     <col width="45" customWidth="1" min="28" max="28"/>
     <col width="45" customWidth="1" min="29" max="29"/>
-    <col width="45" customWidth="1" min="30" max="30"/>
+    <col width="40" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="40" customWidth="1" min="32" max="32"/>
     <col width="40" customWidth="1" min="33" max="33"/>
@@ -539,152 +539,152 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Mag Kalib Yüklenmesi</t>
+          <t>Kalibrasyon - Config Kontrol Sonucu</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Kalibrasyon - Config Kontrol Sonucu</t>
+          <t>Hard Reset - 1 Sonucu:</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Hard Reset - 1 Sonucu:</t>
+          <t>Hard Reset - 2 Sonucu:</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Hard Reset - 2 Sonucu:</t>
+          <t>Soft Reset - 1 Sonucu:</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Soft Reset - 1 Sonucu:</t>
+          <t>Soft Reset - 2 Sonucu:</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Soft Reset - 2 Sonucu:</t>
+          <t>Reset Testi Sonucu:</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Reset Testi Sonucu:</t>
+          <t>Acc Norm Açılış Sonucu:</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Acc Norm Açılış Sonucu:</t>
+          <t>Max Acc Norm Değeri:</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Max Acc Norm Değeri:</t>
+          <t>Min Acc Norm Değeri:</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Min Acc Norm Değeri:</t>
+          <t>Acc Norm Status:</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Acc Norm Status:</t>
+          <t>Gyro Açılış Sonucu:</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Gyro Açılış Sonucu:</t>
+          <t>Acc Döndürme Test - 1 Sonucu:</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Acc Döndürme Test - 1 Sonucu:</t>
+          <t>Acc Döndürme Test - 2 Sonucu:</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Acc Döndürme Test - 2 Sonucu:</t>
+          <t>Acc Döndürme Test - 3 Sonucu:</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Acc Döndürme Test - 3 Sonucu:</t>
+          <t>Acc Döndürme Test - 4 Sonucu:</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Acc Döndürme Test - 4 Sonucu:</t>
+          <t>Acc Döndürme Test - 5 Sonucu:</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Acc Döndürme Test - 5 Sonucu:</t>
+          <t>Acc Döndürme Test - 6 Sonucu:</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Acc Döndürme Test - 6 Sonucu:</t>
+          <t>Acc Döndürme Test Sonucu:</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Acc Döndürme Test Sonucu:</t>
+          <t>Konum 1 Roll Ortalaması:</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Konum 1 Roll Ortalaması:</t>
+          <t>Konum 1 Pitch Ortalaması:</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Konum 1 Pitch Ortalaması:</t>
+          <t>Konum 2 Roll Ortalaması:</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Konum 2 Roll Ortalaması:</t>
+          <t>Konum 2 Pitch Ortalaması:</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Konum 2 Pitch Ortalaması:</t>
+          <t>Konum 3 Roll Ortalaması:</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Konum 3 Roll Ortalaması:</t>
+          <t>Konum 3 Pitch Ortalaması:</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Konum 3 Pitch Ortalaması:</t>
+          <t>Euler Test Sonucu:</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Euler Test Sonucu:</t>
+          <t>Gyro Z Testi Yaw Farkı:</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Gyro Z Testi Yaw Farkı:</t>
+          <t>Gyro Z Test Sonucu:</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Gyro Z Test Sonucu:</t>
+          <t>RS 232 Bağlantı Sonucu:</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>RS 232 Bağlantı Sonucu:</t>
+          <t>RS 422 Bağlantı Sonucu:</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>RS 422 Bağlantı Sonucu:</t>
+          <t>RS 232-422 Bağlantı Sonucu:</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
@@ -779,14 +779,19 @@
           <t>Yüklü Olmalı</t>
         </is>
       </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>9.82</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="U2" s="1" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>Best veya Noted</t>
         </is>
       </c>
       <c r="V2" s="1" t="inlineStr">
@@ -794,6 +799,11 @@
           <t>Best veya Noted</t>
         </is>
       </c>
+      <c r="AD2" s="1" t="inlineStr">
+        <is>
+          <t>0.15'ten küçük olmalı:</t>
+        </is>
+      </c>
       <c r="AE2" s="1" t="inlineStr">
         <is>
           <t>0.15'ten küçük olmalı:</t>
@@ -801,27 +811,27 @@
       </c>
       <c r="AF2" s="1" t="inlineStr">
         <is>
+          <t>89.85 - 90 aralığında olmalı:</t>
+        </is>
+      </c>
+      <c r="AG2" s="1" t="inlineStr">
+        <is>
           <t>0.15'ten küçük olmalı:</t>
         </is>
       </c>
-      <c r="AG2" s="1" t="inlineStr">
-        <is>
-          <t>89.85 - 90 aralığında olmalı:</t>
-        </is>
-      </c>
       <c r="AH2" s="1" t="inlineStr">
         <is>
+          <t>179.85 - 180 aralığında olmalı:</t>
+        </is>
+      </c>
+      <c r="AI2" s="1" t="inlineStr">
+        <is>
           <t>0.15'ten küçük olmalı:</t>
         </is>
       </c>
-      <c r="AI2" s="1" t="inlineStr">
-        <is>
-          <t>179.85 - 180 aralığında olmalı:</t>
-        </is>
-      </c>
       <c r="AJ2" s="1" t="inlineStr">
         <is>
-          <t>0.15'ten küçük olmalı:</t>
+          <t>0.3'ten küçük olmalı:</t>
         </is>
       </c>
       <c r="AK2" s="1" t="inlineStr">
@@ -852,7 +862,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46297.47664075645</v>
+        <v>46297.47664075231</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
@@ -1058,7 +1068,365 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>25325220</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46301.54177081019</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SN Eşleşti</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FW Eşleşti</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DN Eşleşti</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>HW Eşleşti</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Acc Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Gyro Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>9.787121378148397</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9.787121378148397</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.5440277392967192</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.5438781850456846</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.5441290786805101</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.5533561066344436</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.5475784544402469</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.5495018683445645</v>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1940045596629352</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>25325220</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46301.56388732705</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SN Eşleşti</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FW Eşleşti</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DN Eşleşti</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>HW Eşleşti</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Acc Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Gyro Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>9.78903297512465</v>
+      </c>
+      <c r="U5" t="n">
+        <v>9.78903297512465</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.5467747542937083</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.5482196819863102</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.5376591211436257</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.5396669739070354</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.5471154508384267</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.5398845055337164</v>
+      </c>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.09310062775509359</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Test Sonuclari/TestSonuclari.xlsx
+++ b/Test Sonuclari/TestSonuclari.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46301.56388732705</v>
+        <v>46301.56388732639</v>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
@@ -1426,7 +1426,186 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>25325220</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46302.57943053277</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SN Eşleşti</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FW Eşleşti</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DN Eşleşti</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>HW Eşleşti</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Acc Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Gyro Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>9.786487106238226</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9.786487106238226</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.7411853723690729</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.7961936378820763</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>89.5630185158027</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.9904813234822637</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>179.352696103914</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0.9211428801055223</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.02342267303048262</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Test Sonuclari/TestSonuclari.xlsx
+++ b/Test Sonuclari/TestSonuclari.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46302.57943053277</v>
+        <v>46302.57943053241</v>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
@@ -1605,7 +1605,723 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>25325220</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46302.59383635416</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SN Eşleşti</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FW Eşleşti</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DN Eşleşti</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>HW Eşleşti</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Acc Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Gyro Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>9.787005439805871</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9.787005439805871</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.6995720837765331</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.7901309723361938</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.7022732315718767</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.7907501418383468</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.7022078193639293</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.7942021573136695</v>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1384915967710975</v>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>25325220</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46302.60417862269</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SN Eşleşti</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FW Eşleşti</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DN Eşleşti</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>HW Eşleşti</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Acc Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Gyro Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>9.787126902321884</v>
+      </c>
+      <c r="U8" t="n">
+        <v>9.787126902321884</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.6238826688872396</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.7868950949214255</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.6265121399959722</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.7705172827664967</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.6311216787464065</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.7710434465964008</v>
+      </c>
+      <c r="AK8" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.05739642757120618</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>25325220</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>46302.74164277778</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SN Eşleşti</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FW Eşleşti</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DN Eşleşti</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>HW Eşleşti</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Acc Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Gyro Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>9.785986243929019</v>
+      </c>
+      <c r="U9" t="n">
+        <v>9.785986243929019</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.8860533213492099</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.8231434108053975</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.9014239386235411</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.8185690225930029</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.8961810179121741</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.8076660920264279</v>
+      </c>
+      <c r="AK9" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.04722429478897416</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>25325220</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46303.33449379653</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SN Eşleşti</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FW Eşleşti</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DN Eşleşti</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>HW Eşleşti</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Acc Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Gyro Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>9.784762552012126</v>
+      </c>
+      <c r="U10" t="n">
+        <v>9.784762552012126</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.8130748346747488</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.9169657727103883</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>89.35037587269703</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.9969957441848238</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>179.3251373801629</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-1.096682278501523</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1248054988771297</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Test Sonuclari/TestSonuclari.xlsx
+++ b/Test Sonuclari/TestSonuclari.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46303.33449379653</v>
+        <v>46303.3344937963</v>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr"/>
@@ -2321,7 +2321,544 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>25325220</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46303.42198688658</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SN Eşleşti</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FW Eşleşti</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>DN Eşleşti</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>HW Eşleşti</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Acc Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Gyro Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>9.787941626842983</v>
+      </c>
+      <c r="U11" t="n">
+        <v>9.787941626842983</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.7917265981868761</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.9076723297944792</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>89.40019733874813</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-1.021998878445057</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>179.2142271641856</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.9922555028451032</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.07019512212953963</v>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>25325220</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46303.44226603009</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SN Eşleşti</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FW Eşleşti</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>DN Eşleşti</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>HW Eşleşti</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Acc Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Gyro Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>9.786481861931639</v>
+      </c>
+      <c r="U12" t="n">
+        <v>9.786481861931639</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.524492235718313</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-1.040333464109247</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.5358924716805991</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.04405614614115</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.5299290636595839</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-1.042382204181358</v>
+      </c>
+      <c r="AK12" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.0952379431044682</v>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>25325220</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46303.45223095614</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SN Eşleşti</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FW Eşleşti</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>DN Eşleşti</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>HW Eşleşti</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Acc Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Gyro Kalib Yüklü</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>9.787467276535901</v>
+      </c>
+      <c r="U13" t="n">
+        <v>9.787467276535901</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.5236135776998196</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-1.045305978603783</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.5264320010580532</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-1.041063766923167</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.5226893207056006</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-1.053381375221858</v>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.1623870806474748</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Geçti</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>Kaldı</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
